--- a/media/temp_prices_1.xlsx
+++ b/media/temp_prices_1.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -477,13 +477,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -685,13 +685,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -799,13 +799,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -903,13 +903,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1079,13 +1079,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1183,13 +1183,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1391,13 +1391,13 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1619,13 +1619,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1951,13 +1951,13 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2065,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2491,13 +2491,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2719,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3405,13 +3405,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3447,13 +3447,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3887,13 +3887,13 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1.442</v>
+        <v>1.436</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3971,13 +3971,13 @@
         <v>0</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4139,13 +4139,13 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4307,13 +4307,13 @@
         <v>0</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         <v>0.04</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4609,13 +4609,13 @@
         <v>0.04</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4651,13 +4651,13 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4945,13 +4945,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1.452</v>
+        <v>1.446</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5029,13 +5029,13 @@
         <v>0.03</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         <v>0.03</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5449,13 +5449,13 @@
         <v>0.03</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -5659,13 +5659,13 @@
         <v>0.03</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -5869,13 +5869,13 @@
         <v>0.03</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -6079,13 +6079,13 @@
         <v>0.03</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6289,13 +6289,13 @@
         <v>0.03</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6499,13 +6499,13 @@
         <v>0.03</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -6709,13 +6709,13 @@
         <v>0.03</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -6919,13 +6919,13 @@
         <v>0.03</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -7129,13 +7129,13 @@
         <v>0.03</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H143" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -7339,13 +7339,13 @@
         <v>0.03</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H148" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -7549,13 +7549,13 @@
         <v>0.03</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H153" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -7759,13 +7759,13 @@
         <v>0.03</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H158" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -7969,13 +7969,13 @@
         <v>0.03</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -8179,13 +8179,13 @@
         <v>0.03</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -8389,13 +8389,13 @@
         <v>0.03</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -8599,13 +8599,13 @@
         <v>0.03</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -8809,13 +8809,13 @@
         <v>0.03</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -9019,13 +9019,13 @@
         <v>0.03</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -9229,13 +9229,13 @@
         <v>0.03</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -9439,13 +9439,13 @@
         <v>0.03</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H198" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -9649,13 +9649,13 @@
         <v>0.03</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H203" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -9859,13 +9859,13 @@
         <v>0.03</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H208" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -10069,13 +10069,13 @@
         <v>0.03</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -10279,13 +10279,13 @@
         <v>0.03</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H218" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         </is>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         <v>0.03</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H223" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         </is>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -10699,13 +10699,13 @@
         <v>0.03</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H228" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         </is>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         </is>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -10909,13 +10909,13 @@
         <v>0.03</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H233" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         </is>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -11119,13 +11119,13 @@
         <v>0.03</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H238" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -11329,13 +11329,13 @@
         <v>0.05</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H243" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         </is>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -11497,13 +11497,13 @@
         <v>0.03</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H247" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         </is>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -11707,13 +11707,13 @@
         <v>0.03</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H252" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         </is>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -11917,13 +11917,13 @@
         <v>0.05</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H257" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -12001,13 +12001,13 @@
         <v>0.03</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H259" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         </is>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -12334,13 +12334,13 @@
         <v>0</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H267" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>1.432</v>
+        <v>1.426</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -12438,23 +12438,13 @@
         <v>0</v>
       </c>
       <c r="G269" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H269" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>1.422</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>v.nikolova@gtapetroleum.com</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>checho84@abv.bg</t>
-        </is>
+        <v>1.416</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -12474,7 +12464,7 @@
         </is>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -12498,16 +12488,6 @@
       <c r="I270" s="2" t="n">
         <v>1.379</v>
       </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>v.nikolova@gtapetroleum.com</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>checho84@abv.bg</t>
-        </is>
-      </c>
       <c r="O270" t="inlineStr">
         <is>
           <t>205091212</t>
@@ -12526,7 +12506,7 @@
         </is>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -12542,13 +12522,13 @@
         <v>0.03</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="H271" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>1.412</v>
+        <v>1.406</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -12568,7 +12548,7 @@
         </is>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -12610,7 +12590,7 @@
         </is>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -12652,7 +12632,7 @@
         </is>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -12694,7 +12674,7 @@
         </is>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
